--- a/Student_Report.xlsx
+++ b/Student_Report.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Student Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,9 +427,9 @@
           <t>Marks</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Result</t>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Report</t>
         </is>
       </c>
     </row>
@@ -442,11 +442,6 @@
       <c r="B2" t="n">
         <v>95</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -457,11 +452,6 @@
       <c r="B3" t="n">
         <v>90</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -471,11 +461,6 @@
       </c>
       <c r="B4" t="n">
         <v>82</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
       </c>
     </row>
   </sheetData>
